--- a/mosip_master/xlsx/template.xlsx
+++ b/mosip_master/xlsx/template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\Sao-Tome-mosip-master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\eclipse-workspace\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{006C65DA-DB05-43D3-9D2E-FBEA75D66CFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E4D8360-2269-4F1B-9F67-98775B52676C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$Q$171</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <extLst>
@@ -2040,107 +2040,6 @@
   </si>
   <si>
     <t>Modelo de consentimento de registro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;!DOCTYPE html&gt;
-&lt;html lang="pt"&gt;
-&lt;head&gt;
-    &lt;meta charset="UTF-8"&gt;
-    &lt;meta name="viewport" content="width=device-width, initial-scale=1.0"&gt;
-    &lt;title&gt;Termos e CondiÃ§Ãµes&lt;/title&gt;
-    &lt;style&gt;
-        body {
-            font-family: Arial, sans-serif;
-            line-height: 1.6;
-            margin: 20px;
-            text-align: justify;
-        }
-        h1 {
-            text-align: center;
-            color: #333;
-        }
-        h2, h3 {
-            color: #333;
-        }
-        ul {
-            list-style-type: none;
-            padding: 0;
-        }
-        ul li {
-            margin-bottom: 10px;
-        }
-        .section {
-            margin-bottom: 20px;
-        }
-    &lt;/style&gt;
-&lt;/head&gt;
-&lt;body&gt;
-    &lt;h1&gt;Termos e CondiÃ§Ãµes&lt;/h1&gt;
-    &lt;div class="section"&gt;
-        &lt;p&gt;O Modular Open Source Identity Platform (MOSIP) Ã© uma plataforma online que permite que os usuÃ¡rios faÃ§am o prÃ©-registro para fins de identificaÃ§Ã£o nacional. Como parte do Piloto de IdentificaÃ§Ã£o Nacional, o MOSIP estÃ¡ sendo gerido pelo Departamento de E-GovernanÃ§a e DigitalizaÃ§Ã£o (EGDD).&lt;/p&gt;
-        &lt;p&gt;O MOSIP sÃ³ pode ser acessado apÃ³s a aceitaÃ§Ã£o dos termos e condiÃ§Ãµes descritos abaixo.&lt;/p&gt;
-        &lt;p&gt;O acesso Ã© destinado a usuÃ¡rios com pelo menos 16 anos de idade. Pessoas com menos de 16 anos nÃ£o tÃªm permissÃ£o para acessar e usar o Sistema e seu ConteÃºdo.&lt;/p&gt;
-    &lt;/div&gt;
-    &lt;div class="section"&gt;
-        &lt;h3&gt;PropÃ³sito e Escopo&lt;/h3&gt;
-        &lt;p&gt;O uso das informaÃ§Ãµes fornecidas pelo MOSIP Ã© limitado apenas ao uso pessoal. VocÃª pode baixar o ConteÃºdo disponÃ­vel publicamente deste Sistema apenas para uso pessoal e nÃ£o comercial, desde que mantenha intactos todos os avisos de direitos autorais e outras notificaÃ§Ãµes de propriedade.&lt;/p&gt;
-    &lt;/div&gt;
-    &lt;div class="section"&gt;
-        &lt;h3&gt;RestriÃ§Ãµes de Acesso e Uso&lt;/h3&gt;
-        &lt;p&gt;Este Sistema e seu ConteÃºdo sÃ£o protegidos por direitos autorais e outros direitos de propriedade intelectual e de propriedade aplicÃ¡veis.&lt;/p&gt;
-        &lt;p&gt;Ao acessar ou utilizar este Sistema e seu ConteÃºdo, vocÃª concorda em cumprir estes Termos e CondiÃ§Ãµes, bem como quaisquer leis, regras, regulamentos e ordens judiciais aplicÃ¡veis.&lt;/p&gt;
-        &lt;p&gt;VocÃª nÃ£o adquirirÃ¡ quaisquer direitos de propriedade sobre o ConteÃºdo ou este Sistema ao acessar o Sistema e seu ConteÃºdo ou ao utilizar seus ServiÃ§os.&lt;/p&gt;
-    &lt;/div&gt;
-    &lt;div class="section"&gt;
-        &lt;h3&gt;CompreensÃ£o e AceitaÃ§Ã£o dos Termos e CondiÃ§Ãµes pelo Solicitante&lt;/h3&gt;
-        &lt;p&gt;Ao acessar o Sistema e seu ConteÃºdo, vocÃª concorda que leu, entendeu e aceitou ser vinculado pelos Termos e CondiÃ§Ãµes descritos aqui e concorda que:&lt;/p&gt;
-        &lt;ul&gt;
-            &lt;li&gt;1. Compreende e aceita que, a qualquer momento e sem aviso prÃ©vio, o conteÃºdo, requisitos e/ou serviÃ§os do MOSIP podem ser modificados, atualizados ou descontinuados.&lt;/li&gt;
-            &lt;li&gt;2. Compreende e aceita que o EGDD Ã© responsÃ¡vel por garantir a consistÃªncia entre os dados fornecidos a ele e os que registra/divulga, mas nÃ£o tem responsabilidade sobre a veracidade dos mesmos.&lt;/li&gt;
-            &lt;li&gt;3. Declara com veracidade que Ã© responsÃ¡vel por compartilhar informaÃ§Ãµes vÃ¡lidas e verdadeiras.&lt;/li&gt;
-            &lt;li&gt;4. Compreende e aceita que qualquer violaÃ§Ã£o deste acordo por sua parte dÃ¡ ao EGDD o direito automÃ¡tico de iniciar aÃ§Ãµes legais contra vocÃª como consequÃªncia direta de sua violaÃ§Ã£o.&lt;/li&gt;
-            &lt;li&gt;5. Compreende e aceita que quaisquer aÃ§Ãµes tomadas pelo EGDD sob a clÃ¡usula 4 sÃ£o resultado do dever de cuidado para com todos os usuÃ¡rios deste Sistema e da proteÃ§Ã£o de todas as informaÃ§Ãµes pessoais nele contidas.&lt;/li&gt;
-            &lt;li&gt;6. Compreende e aceita que o EGDD estÃ¡ sempre preocupado em garantir os mais altos padrÃµes de qualidade, transparÃªncia, proteÃ§Ã£o e confidencialidade de todas as informaÃ§Ãµes e em defendÃª-las por meio do devido processo em quaisquer procedimentos legais.&lt;/li&gt;
-        &lt;/ul&gt;
-    &lt;/div&gt;
-    &lt;div class="section"&gt;
-        &lt;h3&gt;RescisÃ£o&lt;/h3&gt;
-        &lt;p&gt;Seu acesso e uso do Sistema e do ConteÃºdo podem ser encerrados a qualquer momento sem aviso prÃ©vio. VocÃª nÃ£o deve realizar nenhuma das seguintes aÃ§Ãµes:&lt;/p&gt;
-        &lt;ul&gt;
-            &lt;li&gt;i. Violar quaisquer leis aplicÃ¡veis de Belize (incluindo, mas nÃ£o se limitando Ã  Lei de ProteÃ§Ã£o de Dados, Lei de Liberdade de InformaÃ§Ã£o, Lei de Crimes CibernÃ©ticos, etc.), direitos autorais e outros direitos de propriedade intelectual ou de propriedade sobre o Sistema ou seu ConteÃºdo;&lt;/li&gt;
-            &lt;li&gt;ii. Engajar-se em mineraÃ§Ã£o de dados ou usar "bots" ou ferramentas ou mÃ©todos semelhantes de coleta e extraÃ§Ã£o de dados em conexÃ£o com o Sistema ou seu ConteÃºdo;&lt;/li&gt;
-            &lt;li&gt;iii. Descompilar, fazer engenharia reversa, desmontar, alugar, vender, distribuir ou reproduzir o Sistema;&lt;/li&gt;
-            &lt;li&gt;iv. Falsificar sua afiliaÃ§Ã£o ou se passar por qualquer pessoa ou entidade;&lt;/li&gt;
-            &lt;li&gt;v. Falsificar o ConteÃºdo ou o Sistema, ou informar incorretamente outros sobre a origem ou propriedade do ConteÃºdo ou do Sistema.&lt;/li&gt;
-        &lt;/ul&gt;
-        &lt;p&gt;Seu acesso e uso deste Sistema podem ser monitorados, inclusive, mas nÃ£o se limitando, para o propÃ³sito de identificar atividades ilegais ou nÃ£o autorizadas.&lt;/p&gt;
-    &lt;/div&gt;
-    &lt;div class="section"&gt;
-        &lt;h3&gt;IsenÃ§Ã£o de Responsabilidade&lt;/h3&gt;
-        &lt;p&gt;O EGDD nÃ£o serÃ¡ responsÃ¡vel por:&lt;/p&gt;
-        &lt;ul&gt;
-            &lt;li&gt;a. Qualquer uso indevido ou incorreto das informaÃ§Ãµes descritas e/ou contidas neste documento; ou&lt;/li&gt;
-            &lt;li&gt;b. Quaisquer danos diretos, indiretos, incidentais, especiais, exemplares ou consequentes (incluindo, mas nÃ£o se limitando a aquisiÃ§Ã£o ou substituiÃ§Ã£o de bens ou serviÃ§os; perda de uso, dados ou lucros; ou interrupÃ§Ã£o de negÃ³cios) causados de qualquer forma e em qualquer teoria de responsabilidade, seja em contrato, responsabilidade estrita ou ato ilÃ­cito (incluindo negligÃªncia ou outra) resultante de qualquer forma do uso deste sistema, mesmo que avisado sobre a possibilidade de tais danos.&lt;/li&gt;
-        &lt;/ul&gt;
-        &lt;p&gt;Esta isenÃ§Ã£o de responsabilidade aplica-se a quaisquer danos ou lesÃµes, incluindo, mas nÃ£o se limitando, Ã queles causados por qualquer falha de desempenho, erro, omissÃ£o, interrupÃ§Ã£o, exclusÃ£o, defeito, atraso na operaÃ§Ã£o ou transmissÃ£o, vÃ­rus de computador, infecÃ§Ãµes por malware, falha na linha de comunicaÃ§Ã£o, roubo ou destruiÃ§Ã£o ou acesso nÃ£o autorizado, alteraÃ§Ã£o ou uso de registros, seja por violaÃ§Ã£o de contrato, comportamento ilÃ­cito, negligÃªncia ou outra causa de aÃ§Ã£o.&lt;/p&gt;
-    &lt;/div&gt;
-    &lt;div class="section"&gt;
-        &lt;h3&gt;IsenÃ§Ã£o de Garantia/PrecisÃ£o dos Dados&lt;/h3&gt;
-        &lt;p&gt;O EGDD fornece todas as informaÃ§Ãµes recebidas por ele em uma base "como estÃ¡". Embora os dados encontrados no Sistema tenham sido produzidos e processados a partir de fontes consideradas confiÃ¡veis, nenhuma garantia expressa ou implÃ­cita Ã© feita quanto Ã  precisÃ£o, adequaÃ§Ã£o, integridade, legalidade, confiabilidade ou utilidade de qualquer informaÃ§Ã£o. Esta isenÃ§Ã£o de responsabilidade aplica-se tanto aos usos isolados quanto agregados das informaÃ§Ãµes. Todas as garantias de qualquer tipo, expressas ou implÃ­citas, incluindo, mas nÃ£o se limitando Ã s garantias implÃ­citas de comercializaÃ§Ã£o, adequaÃ§Ã£o a um propÃ³sito especÃ­fico, isenÃ§Ã£o de contaminaÃ§Ã£o por vÃ­rus de computador e nÃ£o violaÃ§Ã£o de direitos de propriedade, SÃƒO ISENTAS. MudanÃ§as podem ser periodicamente adicionadas Ã s informaÃ§Ãµes aqui contidas; essas mudanÃ§as podem ou nÃ£o ser incorporadas em qualquer nova versÃ£o da publicaÃ§Ã£o. Se vocÃª obteve informaÃ§Ãµes do Sistema de uma fonte que nÃ£o seja o Sistema, esteja ciente de que os dados eletrÃ´nicos podem ser alterados apÃ³s a distribuiÃ§Ã£o original. Os dados tambÃ©m podem se tornar desatualizados rapidamente. Ã‰ recomendÃ¡vel prestar atenÃ§Ã£o cuidadosa ao conteÃºdo de qualquer metadado associado a um arquivo e que o originador dos dados ou informaÃ§Ãµes seja contatado com quaisquer dÃºvidas sobre o uso apropriado.&lt;/p&gt;
-    &lt;/div&gt;
-    &lt;div class="section"&gt;
-        &lt;h3&gt;ReclamaÃ§Ãµes de Terceiros&lt;/h3&gt;
-        &lt;p&gt;O EGDD distribui conteÃºdo, Ã s vezes fornecido por terceiros e usuÃ¡rios. Quaisquer opiniÃµes, conselhos, declaraÃ§Ãµes, serviÃ§os, ofertas ou outras informaÃ§Ãµes ou conteÃºdos expressos ou disponibilizados por terceiros, incluindo provedores de informaÃ§Ãµes, usuÃ¡rios ou outros, sÃ£o de responsabilidade dos respectivos autores ou distribuidores e nÃ£o refletem necessariamente as opiniÃµes do Sistema.&lt;/p&gt;
-        &lt;p&gt;O EGDD nÃ£o serÃ¡ responsÃ¡vel por quaisquer reclamaÃ§Ãµes ou perdas de terceiros de qualquer natureza, incluindo, mas nÃ£o se limitando a perda de lucros, danos diretos, indiretos, especiais ou consequentes resultantes do uso ou da incapacidade de usar o Sistema de acordo com os termos e condiÃ§Ãµes estabelecidos aqui.&lt;/p&gt;
-    &lt;/div&gt;
-    &lt;div class="section"&gt;
-        &lt;h3&gt;ResoluÃ§Ã£o de Disputas&lt;/h3&gt;
-        &lt;p&gt;A interpretaÃ§Ã£o das isenÃ§Ãµes de responsabilidade acima e a resoluÃ§Ã£o de disputas sÃ£o regidas pelas leis de Belize.&lt;/p&gt;
-		&lt;p&gt;Para informaÃ§Ãµes adicionais, entre em contato com o EGDD via e-mail em info@inic.gov.st.&lt;/p&gt;
-    &lt;/div&gt;
-&lt;/body&gt;
-&lt;/html&gt;
-</t>
   </si>
   <si>
     <t>Reimprimir e-mail de sucesso de validaÃ§Ã£o de pacote</t>
@@ -2914,6 +2813,9 @@
   <si>
     <t>Registration Consent</t>
   </si>
+  <si>
+    <t>&lt;!DOCTYPE html&gt;&lt;html&gt;&lt;head&gt;&lt;title&gt;Consent&lt;/title&gt;&lt;/head&gt;&lt;body&gt;&lt;div&gt;Entendo que os dados coletados a meu respeito durante o cadastro pela referida autoridade incluem &lt;br&gt;&lt;br&gt;&amp;#x2022 Nome &lt;br&gt; &amp;#x2022 Data de nascimento &lt;br&gt; &amp;#x2022 Gênero &lt;br&gt; &amp;#x2022 Endereço &lt;br&gt; &amp;#x2022 Detalhes de contato &lt;br&gt; &amp;#x2022 Documentos&lt;br&gt; &amp;#x2022 Biometria &lt;br&gt; &lt;br&gt;Compreendo também que estas informações serão armazenadas e processadas com o objetivo de verificar a minha identidade para aceder a diversos serviços ou para cumprir uma obrigação legal. Dou o meu consentimento para a recolha destes dados para este fim.&lt;/div&gt;&lt;/body&gt;&lt;/html&gt;</t>
+  </si>
 </sst>
 </file>
 
@@ -3337,13 +3239,13 @@
         <v>209</v>
       </c>
       <c r="M2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N2" t="s">
         <v>208</v>
       </c>
       <c r="O2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P2" t="b">
         <v>0</v>
@@ -3390,13 +3292,13 @@
         <v>209</v>
       </c>
       <c r="M3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N3" t="s">
         <v>208</v>
       </c>
       <c r="O3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P3" t="b">
         <v>0</v>
@@ -3443,13 +3345,13 @@
         <v>209</v>
       </c>
       <c r="M4" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N4" t="s">
         <v>208</v>
       </c>
       <c r="O4" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P4" t="b">
         <v>0</v>
@@ -3496,13 +3398,13 @@
         <v>209</v>
       </c>
       <c r="M5" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N5" t="s">
         <v>208</v>
       </c>
       <c r="O5" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P5" t="b">
         <v>0</v>
@@ -3549,13 +3451,13 @@
         <v>209</v>
       </c>
       <c r="M6" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N6" t="s">
         <v>207</v>
       </c>
       <c r="O6" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P6" t="b">
         <v>0</v>
@@ -3602,13 +3504,13 @@
         <v>209</v>
       </c>
       <c r="M7" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N7" t="s">
         <v>208</v>
       </c>
       <c r="O7" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P7" t="b">
         <v>0</v>
@@ -3655,13 +3557,13 @@
         <v>209</v>
       </c>
       <c r="M8" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N8" t="s">
         <v>208</v>
       </c>
       <c r="O8" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P8" t="b">
         <v>0</v>
@@ -3708,13 +3610,13 @@
         <v>209</v>
       </c>
       <c r="M9" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N9" t="s">
         <v>208</v>
       </c>
       <c r="O9" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P9" t="b">
         <v>0</v>
@@ -3761,13 +3663,13 @@
         <v>209</v>
       </c>
       <c r="M10" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N10" t="s">
         <v>208</v>
       </c>
       <c r="O10" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P10" t="b">
         <v>0</v>
@@ -3814,13 +3716,13 @@
         <v>209</v>
       </c>
       <c r="M11" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N11" t="s">
         <v>208</v>
       </c>
       <c r="O11" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P11" t="b">
         <v>0</v>
@@ -3867,13 +3769,13 @@
         <v>209</v>
       </c>
       <c r="M12" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N12" t="s">
         <v>208</v>
       </c>
       <c r="O12" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P12" t="b">
         <v>0</v>
@@ -3920,13 +3822,13 @@
         <v>209</v>
       </c>
       <c r="M13" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N13" t="s">
         <v>208</v>
       </c>
       <c r="O13" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P13" t="b">
         <v>0</v>
@@ -3973,13 +3875,13 @@
         <v>209</v>
       </c>
       <c r="M14" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N14" t="s">
         <v>208</v>
       </c>
       <c r="O14" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P14" t="b">
         <v>0</v>
@@ -4026,13 +3928,13 @@
         <v>209</v>
       </c>
       <c r="M15" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N15" t="s">
         <v>208</v>
       </c>
       <c r="O15" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P15" t="b">
         <v>0</v>
@@ -4079,13 +3981,13 @@
         <v>209</v>
       </c>
       <c r="M16" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N16" t="s">
         <v>207</v>
       </c>
       <c r="O16" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P16" t="b">
         <v>0</v>
@@ -4132,13 +4034,13 @@
         <v>209</v>
       </c>
       <c r="M17" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N17" t="s">
         <v>208</v>
       </c>
       <c r="O17" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P17" t="b">
         <v>0</v>
@@ -4185,13 +4087,13 @@
         <v>209</v>
       </c>
       <c r="M18" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N18" t="s">
         <v>208</v>
       </c>
       <c r="O18" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P18" t="b">
         <v>0</v>
@@ -4238,13 +4140,13 @@
         <v>209</v>
       </c>
       <c r="M19" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N19" t="s">
         <v>208</v>
       </c>
       <c r="O19" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P19" t="b">
         <v>0</v>
@@ -4291,13 +4193,13 @@
         <v>209</v>
       </c>
       <c r="M20" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N20" t="s">
         <v>208</v>
       </c>
       <c r="O20" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P20" t="b">
         <v>0</v>
@@ -4344,13 +4246,13 @@
         <v>209</v>
       </c>
       <c r="M21" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N21" t="s">
         <v>208</v>
       </c>
       <c r="O21" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P21" t="b">
         <v>0</v>
@@ -4397,13 +4299,13 @@
         <v>209</v>
       </c>
       <c r="M22" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N22" t="s">
         <v>208</v>
       </c>
       <c r="O22" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P22" t="b">
         <v>0</v>
@@ -4450,13 +4352,13 @@
         <v>209</v>
       </c>
       <c r="M23" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N23" t="s">
         <v>208</v>
       </c>
       <c r="O23" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P23" t="b">
         <v>0</v>
@@ -4503,13 +4405,13 @@
         <v>209</v>
       </c>
       <c r="M24" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N24" t="s">
         <v>207</v>
       </c>
       <c r="O24" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P24" t="b">
         <v>0</v>
@@ -4556,13 +4458,13 @@
         <v>209</v>
       </c>
       <c r="M25" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N25" t="s">
         <v>208</v>
       </c>
       <c r="O25" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P25" t="b">
         <v>0</v>
@@ -4609,13 +4511,13 @@
         <v>209</v>
       </c>
       <c r="M26" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N26" t="s">
         <v>208</v>
       </c>
       <c r="O26" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P26" t="b">
         <v>0</v>
@@ -4662,13 +4564,13 @@
         <v>209</v>
       </c>
       <c r="M27" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N27" t="s">
         <v>208</v>
       </c>
       <c r="O27" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P27" t="b">
         <v>0</v>
@@ -4715,13 +4617,13 @@
         <v>209</v>
       </c>
       <c r="M28" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N28" t="s">
         <v>208</v>
       </c>
       <c r="O28" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P28" t="b">
         <v>0</v>
@@ -4768,13 +4670,13 @@
         <v>209</v>
       </c>
       <c r="M29" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N29" t="s">
         <v>208</v>
       </c>
       <c r="O29" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P29" t="b">
         <v>0</v>
@@ -4821,13 +4723,13 @@
         <v>209</v>
       </c>
       <c r="M30" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N30" t="s">
         <v>208</v>
       </c>
       <c r="O30" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P30" t="b">
         <v>0</v>
@@ -4874,13 +4776,13 @@
         <v>209</v>
       </c>
       <c r="M31" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N31" t="s">
         <v>208</v>
       </c>
       <c r="O31" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P31" t="b">
         <v>0</v>
@@ -4927,13 +4829,13 @@
         <v>209</v>
       </c>
       <c r="M32" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N32" t="s">
         <v>208</v>
       </c>
       <c r="O32" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P32" t="b">
         <v>0</v>
@@ -4980,13 +4882,13 @@
         <v>209</v>
       </c>
       <c r="M33" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N33" t="s">
         <v>224</v>
       </c>
       <c r="O33" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P33" t="b">
         <v>0</v>
@@ -5033,13 +4935,13 @@
         <v>209</v>
       </c>
       <c r="M34" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N34" t="s">
         <v>208</v>
       </c>
       <c r="O34" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P34" t="b">
         <v>0</v>
@@ -5086,13 +4988,13 @@
         <v>209</v>
       </c>
       <c r="M35" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N35" t="s">
         <v>208</v>
       </c>
       <c r="O35" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P35" t="b">
         <v>0</v>
@@ -5139,13 +5041,13 @@
         <v>209</v>
       </c>
       <c r="M36" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N36" t="s">
         <v>208</v>
       </c>
       <c r="O36" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P36" t="b">
         <v>0</v>
@@ -5192,13 +5094,13 @@
         <v>209</v>
       </c>
       <c r="M37" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N37" t="s">
         <v>208</v>
       </c>
       <c r="O37" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P37" t="b">
         <v>0</v>
@@ -5245,13 +5147,13 @@
         <v>209</v>
       </c>
       <c r="M38" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N38" t="s">
         <v>208</v>
       </c>
       <c r="O38" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P38" t="b">
         <v>0</v>
@@ -5298,13 +5200,13 @@
         <v>209</v>
       </c>
       <c r="M39" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N39" t="s">
         <v>208</v>
       </c>
       <c r="O39" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P39" t="b">
         <v>0</v>
@@ -5351,13 +5253,13 @@
         <v>209</v>
       </c>
       <c r="M40" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N40" t="s">
         <v>208</v>
       </c>
       <c r="O40" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P40" t="b">
         <v>0</v>
@@ -5404,13 +5306,13 @@
         <v>209</v>
       </c>
       <c r="M41" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N41" t="s">
         <v>208</v>
       </c>
       <c r="O41" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P41" t="b">
         <v>0</v>
@@ -5457,13 +5359,13 @@
         <v>209</v>
       </c>
       <c r="M42" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N42" t="s">
         <v>208</v>
       </c>
       <c r="O42" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P42" t="b">
         <v>0</v>
@@ -5510,13 +5412,13 @@
         <v>209</v>
       </c>
       <c r="M43" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N43" t="s">
         <v>207</v>
       </c>
       <c r="O43" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P43" t="b">
         <v>0</v>
@@ -5563,13 +5465,13 @@
         <v>209</v>
       </c>
       <c r="M44" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N44" t="s">
         <v>208</v>
       </c>
       <c r="O44" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P44" t="b">
         <v>0</v>
@@ -5616,13 +5518,13 @@
         <v>209</v>
       </c>
       <c r="M45" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N45" t="s">
         <v>208</v>
       </c>
       <c r="O45" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P45" t="b">
         <v>0</v>
@@ -5669,13 +5571,13 @@
         <v>209</v>
       </c>
       <c r="M46" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N46" t="s">
         <v>208</v>
       </c>
       <c r="O46" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P46" t="b">
         <v>0</v>
@@ -5722,13 +5624,13 @@
         <v>209</v>
       </c>
       <c r="M47" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N47" t="s">
         <v>208</v>
       </c>
       <c r="O47" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P47" t="b">
         <v>0</v>
@@ -5775,13 +5677,13 @@
         <v>209</v>
       </c>
       <c r="M48" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N48" t="s">
         <v>208</v>
       </c>
       <c r="O48" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P48" t="b">
         <v>0</v>
@@ -5828,13 +5730,13 @@
         <v>209</v>
       </c>
       <c r="M49" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N49" t="s">
         <v>208</v>
       </c>
       <c r="O49" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P49" t="b">
         <v>0</v>
@@ -5881,13 +5783,13 @@
         <v>209</v>
       </c>
       <c r="M50" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N50" t="s">
         <v>208</v>
       </c>
       <c r="O50" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P50" t="b">
         <v>0</v>
@@ -5934,13 +5836,13 @@
         <v>209</v>
       </c>
       <c r="M51" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N51" t="s">
         <v>208</v>
       </c>
       <c r="O51" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P51" t="b">
         <v>0</v>
@@ -5987,13 +5889,13 @@
         <v>209</v>
       </c>
       <c r="M52" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N52" t="s">
         <v>208</v>
       </c>
       <c r="O52" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P52" t="b">
         <v>0</v>
@@ -6040,13 +5942,13 @@
         <v>209</v>
       </c>
       <c r="M53" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N53" t="s">
         <v>208</v>
       </c>
       <c r="O53" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P53" t="b">
         <v>0</v>
@@ -6093,13 +5995,13 @@
         <v>209</v>
       </c>
       <c r="M54" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N54" t="s">
         <v>208</v>
       </c>
       <c r="O54" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P54" t="b">
         <v>0</v>
@@ -6146,13 +6048,13 @@
         <v>209</v>
       </c>
       <c r="M55" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N55" t="s">
         <v>208</v>
       </c>
       <c r="O55" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P55" t="b">
         <v>0</v>
@@ -6199,13 +6101,13 @@
         <v>209</v>
       </c>
       <c r="M56" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N56" t="s">
         <v>208</v>
       </c>
       <c r="O56" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P56" t="b">
         <v>0</v>
@@ -6252,13 +6154,13 @@
         <v>209</v>
       </c>
       <c r="M57" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N57" t="s">
         <v>208</v>
       </c>
       <c r="O57" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P57" t="b">
         <v>0</v>
@@ -6305,13 +6207,13 @@
         <v>209</v>
       </c>
       <c r="M58" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N58" t="s">
         <v>208</v>
       </c>
       <c r="O58" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P58" t="b">
         <v>0</v>
@@ -6358,13 +6260,13 @@
         <v>209</v>
       </c>
       <c r="M59" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N59" t="s">
         <v>208</v>
       </c>
       <c r="O59" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P59" t="b">
         <v>0</v>
@@ -6411,13 +6313,13 @@
         <v>209</v>
       </c>
       <c r="M60" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N60" t="s">
         <v>208</v>
       </c>
       <c r="O60" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P60" t="b">
         <v>0</v>
@@ -6464,13 +6366,13 @@
         <v>209</v>
       </c>
       <c r="M61" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N61" t="s">
         <v>208</v>
       </c>
       <c r="O61" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P61" t="b">
         <v>0</v>
@@ -6517,13 +6419,13 @@
         <v>209</v>
       </c>
       <c r="M62" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N62" t="s">
         <v>224</v>
       </c>
       <c r="O62" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P62" t="b">
         <v>0</v>
@@ -6570,13 +6472,13 @@
         <v>209</v>
       </c>
       <c r="M63" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N63" t="s">
         <v>208</v>
       </c>
       <c r="O63" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P63" t="b">
         <v>0</v>
@@ -6623,13 +6525,13 @@
         <v>209</v>
       </c>
       <c r="M64" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N64" t="s">
         <v>208</v>
       </c>
       <c r="O64" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P64" t="b">
         <v>0</v>
@@ -6676,13 +6578,13 @@
         <v>209</v>
       </c>
       <c r="M65" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N65" t="s">
         <v>208</v>
       </c>
       <c r="O65" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P65" t="b">
         <v>0</v>
@@ -6729,13 +6631,13 @@
         <v>209</v>
       </c>
       <c r="M66" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N66" t="s">
         <v>208</v>
       </c>
       <c r="O66" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P66" t="b">
         <v>0</v>
@@ -6782,13 +6684,13 @@
         <v>209</v>
       </c>
       <c r="M67" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N67" t="s">
         <v>208</v>
       </c>
       <c r="O67" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P67" t="b">
         <v>0</v>
@@ -6835,13 +6737,13 @@
         <v>209</v>
       </c>
       <c r="M68" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N68" t="s">
         <v>208</v>
       </c>
       <c r="O68" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P68" t="b">
         <v>0</v>
@@ -6888,13 +6790,13 @@
         <v>209</v>
       </c>
       <c r="M69" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N69" t="s">
         <v>208</v>
       </c>
       <c r="O69" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P69" t="b">
         <v>0</v>
@@ -6941,13 +6843,13 @@
         <v>209</v>
       </c>
       <c r="M70" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N70" t="s">
         <v>208</v>
       </c>
       <c r="O70" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P70" t="b">
         <v>0</v>
@@ -6994,13 +6896,13 @@
         <v>209</v>
       </c>
       <c r="M71" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N71" t="s">
         <v>208</v>
       </c>
       <c r="O71" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P71" t="b">
         <v>0</v>
@@ -7047,13 +6949,13 @@
         <v>209</v>
       </c>
       <c r="M72" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N72" t="s">
         <v>208</v>
       </c>
       <c r="O72" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P72" t="b">
         <v>0</v>
@@ -7100,13 +7002,13 @@
         <v>209</v>
       </c>
       <c r="M73" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N73" t="s">
         <v>208</v>
       </c>
       <c r="O73" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P73" t="b">
         <v>0</v>
@@ -7153,13 +7055,13 @@
         <v>209</v>
       </c>
       <c r="M74" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N74" t="s">
         <v>208</v>
       </c>
       <c r="O74" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P74" t="b">
         <v>0</v>
@@ -7206,13 +7108,13 @@
         <v>209</v>
       </c>
       <c r="M75" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N75" t="s">
         <v>208</v>
       </c>
       <c r="O75" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P75" t="b">
         <v>0</v>
@@ -7259,13 +7161,13 @@
         <v>209</v>
       </c>
       <c r="M76" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N76" t="s">
         <v>207</v>
       </c>
       <c r="O76" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P76" t="b">
         <v>0</v>
@@ -7312,13 +7214,13 @@
         <v>209</v>
       </c>
       <c r="M77" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N77" t="s">
         <v>208</v>
       </c>
       <c r="O77" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P77" t="b">
         <v>0</v>
@@ -7365,13 +7267,13 @@
         <v>209</v>
       </c>
       <c r="M78" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N78" t="s">
         <v>208</v>
       </c>
       <c r="O78" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P78" t="b">
         <v>0</v>
@@ -7418,13 +7320,13 @@
         <v>209</v>
       </c>
       <c r="M79" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N79" t="s">
         <v>224</v>
       </c>
       <c r="O79" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P79" t="b">
         <v>0</v>
@@ -7471,13 +7373,13 @@
         <v>209</v>
       </c>
       <c r="M80" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N80" t="s">
         <v>224</v>
       </c>
       <c r="O80" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P80" t="b">
         <v>0</v>
@@ -7524,13 +7426,13 @@
         <v>209</v>
       </c>
       <c r="M81" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N81" t="s">
         <v>208</v>
       </c>
       <c r="O81" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P81" t="b">
         <v>0</v>
@@ -7577,13 +7479,13 @@
         <v>209</v>
       </c>
       <c r="M82" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N82" t="s">
         <v>208</v>
       </c>
       <c r="O82" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P82" t="b">
         <v>0</v>
@@ -7630,13 +7532,13 @@
         <v>209</v>
       </c>
       <c r="M83" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N83" t="s">
         <v>208</v>
       </c>
       <c r="O83" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P83" t="b">
         <v>0</v>
@@ -7683,13 +7585,13 @@
         <v>209</v>
       </c>
       <c r="M84" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N84" t="s">
         <v>224</v>
       </c>
       <c r="O84" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P84" t="b">
         <v>0</v>
@@ -7736,13 +7638,13 @@
         <v>209</v>
       </c>
       <c r="M85" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N85" t="s">
         <v>208</v>
       </c>
       <c r="O85" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P85" t="b">
         <v>0</v>
@@ -7789,13 +7691,13 @@
         <v>209</v>
       </c>
       <c r="M86" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N86" t="s">
         <v>208</v>
       </c>
       <c r="O86" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P86" t="b">
         <v>0</v>
@@ -7842,13 +7744,13 @@
         <v>209</v>
       </c>
       <c r="M87" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N87" t="s">
         <v>208</v>
       </c>
       <c r="O87" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P87" t="b">
         <v>0</v>
@@ -7895,13 +7797,13 @@
         <v>209</v>
       </c>
       <c r="M88" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N88" t="s">
         <v>208</v>
       </c>
       <c r="O88" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P88" t="b">
         <v>0</v>
@@ -7948,13 +7850,13 @@
         <v>209</v>
       </c>
       <c r="M89" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N89" t="s">
         <v>208</v>
       </c>
       <c r="O89" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P89" t="b">
         <v>0</v>
@@ -8001,13 +7903,13 @@
         <v>209</v>
       </c>
       <c r="M90" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N90" t="s">
         <v>208</v>
       </c>
       <c r="O90" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P90" t="b">
         <v>0</v>
@@ -8054,13 +7956,13 @@
         <v>209</v>
       </c>
       <c r="M91" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N91" t="s">
         <v>208</v>
       </c>
       <c r="O91" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P91" t="b">
         <v>0</v>
@@ -8107,13 +8009,13 @@
         <v>209</v>
       </c>
       <c r="M92" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N92" t="s">
         <v>208</v>
       </c>
       <c r="O92" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P92" t="b">
         <v>0</v>
@@ -8160,13 +8062,13 @@
         <v>209</v>
       </c>
       <c r="M93" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N93" t="s">
         <v>208</v>
       </c>
       <c r="O93" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P93" t="b">
         <v>0</v>
@@ -8213,13 +8115,13 @@
         <v>209</v>
       </c>
       <c r="M94" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N94" t="s">
         <v>208</v>
       </c>
       <c r="O94" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P94" t="b">
         <v>0</v>
@@ -8266,13 +8168,13 @@
         <v>209</v>
       </c>
       <c r="M95" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N95" t="s">
         <v>208</v>
       </c>
       <c r="O95" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P95" t="b">
         <v>0</v>
@@ -8319,13 +8221,13 @@
         <v>209</v>
       </c>
       <c r="M96" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N96" t="s">
         <v>208</v>
       </c>
       <c r="O96" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P96" t="b">
         <v>0</v>
@@ -8372,13 +8274,13 @@
         <v>209</v>
       </c>
       <c r="M97" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N97" t="s">
         <v>208</v>
       </c>
       <c r="O97" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P97" t="b">
         <v>0</v>
@@ -8425,13 +8327,13 @@
         <v>209</v>
       </c>
       <c r="M98" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N98" t="s">
         <v>208</v>
       </c>
       <c r="O98" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P98" t="b">
         <v>0</v>
@@ -8478,13 +8380,13 @@
         <v>209</v>
       </c>
       <c r="M99" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N99" t="s">
         <v>208</v>
       </c>
       <c r="O99" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P99" t="b">
         <v>0</v>
@@ -8493,7 +8395,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="100" spans="1:17" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:17" ht="203" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>1269</v>
       </c>
@@ -8510,7 +8412,7 @@
         <v>14</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>399</v>
+        <v>530</v>
       </c>
       <c r="G100">
         <v>10002</v>
@@ -8519,7 +8421,7 @@
         <v>28</v>
       </c>
       <c r="I100" s="6" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="J100" t="s">
         <v>206</v>
@@ -8531,13 +8433,13 @@
         <v>209</v>
       </c>
       <c r="M100" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N100" t="s">
         <v>207</v>
       </c>
       <c r="O100" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P100" t="b">
         <v>0</v>
@@ -8551,19 +8453,19 @@
         <v>1219</v>
       </c>
       <c r="B101" t="s">
+        <v>399</v>
+      </c>
+      <c r="C101" t="s">
+        <v>399</v>
+      </c>
+      <c r="D101" t="s">
+        <v>13</v>
+      </c>
+      <c r="E101" t="s">
+        <v>14</v>
+      </c>
+      <c r="F101" s="3" t="s">
         <v>400</v>
-      </c>
-      <c r="C101" t="s">
-        <v>400</v>
-      </c>
-      <c r="D101" t="s">
-        <v>13</v>
-      </c>
-      <c r="E101" t="s">
-        <v>14</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>401</v>
       </c>
       <c r="G101">
         <v>10003</v>
@@ -8584,13 +8486,13 @@
         <v>209</v>
       </c>
       <c r="M101" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N101" t="s">
         <v>208</v>
       </c>
       <c r="O101" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P101" t="b">
         <v>0</v>
@@ -8604,10 +8506,10 @@
         <v>1200</v>
       </c>
       <c r="B102" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C102" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D102" t="s">
         <v>13</v>
@@ -8637,13 +8539,13 @@
         <v>209</v>
       </c>
       <c r="M102" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N102" t="s">
         <v>208</v>
       </c>
       <c r="O102" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P102" t="b">
         <v>0</v>
@@ -8657,10 +8559,10 @@
         <v>1100</v>
       </c>
       <c r="B103" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C103" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D103" t="s">
         <v>46</v>
@@ -8669,13 +8571,13 @@
         <v>14</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G103">
         <v>10007</v>
       </c>
       <c r="H103" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="I103" t="s">
         <v>223</v>
@@ -8690,13 +8592,13 @@
         <v>209</v>
       </c>
       <c r="M103" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N103" t="s">
         <v>207</v>
       </c>
       <c r="O103" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P103" t="b">
         <v>0</v>
@@ -8710,19 +8612,19 @@
         <v>1102</v>
       </c>
       <c r="B104" t="s">
+        <v>405</v>
+      </c>
+      <c r="C104" t="s">
+        <v>405</v>
+      </c>
+      <c r="D104" t="s">
+        <v>13</v>
+      </c>
+      <c r="E104" t="s">
+        <v>14</v>
+      </c>
+      <c r="F104" t="s">
         <v>406</v>
-      </c>
-      <c r="C104" t="s">
-        <v>406</v>
-      </c>
-      <c r="D104" t="s">
-        <v>13</v>
-      </c>
-      <c r="E104" t="s">
-        <v>14</v>
-      </c>
-      <c r="F104" t="s">
-        <v>407</v>
       </c>
       <c r="G104">
         <v>10004</v>
@@ -8743,13 +8645,13 @@
         <v>209</v>
       </c>
       <c r="M104" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N104" t="s">
         <v>208</v>
       </c>
       <c r="O104" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P104" t="b">
         <v>0</v>
@@ -8763,19 +8665,19 @@
         <v>1107</v>
       </c>
       <c r="B105" t="s">
+        <v>407</v>
+      </c>
+      <c r="C105" t="s">
+        <v>407</v>
+      </c>
+      <c r="D105" t="s">
+        <v>13</v>
+      </c>
+      <c r="E105" t="s">
+        <v>14</v>
+      </c>
+      <c r="F105" s="3" t="s">
         <v>408</v>
-      </c>
-      <c r="C105" t="s">
-        <v>408</v>
-      </c>
-      <c r="D105" t="s">
-        <v>13</v>
-      </c>
-      <c r="E105" t="s">
-        <v>14</v>
-      </c>
-      <c r="F105" s="3" t="s">
-        <v>409</v>
       </c>
       <c r="G105">
         <v>10003</v>
@@ -8796,13 +8698,13 @@
         <v>209</v>
       </c>
       <c r="M105" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N105" t="s">
         <v>208</v>
       </c>
       <c r="O105" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P105" t="b">
         <v>0</v>
@@ -8816,19 +8718,19 @@
         <v>1109</v>
       </c>
       <c r="B106" t="s">
+        <v>409</v>
+      </c>
+      <c r="C106" t="s">
+        <v>409</v>
+      </c>
+      <c r="D106" t="s">
+        <v>13</v>
+      </c>
+      <c r="E106" t="s">
+        <v>14</v>
+      </c>
+      <c r="F106" s="3" t="s">
         <v>410</v>
-      </c>
-      <c r="C106" t="s">
-        <v>410</v>
-      </c>
-      <c r="D106" t="s">
-        <v>13</v>
-      </c>
-      <c r="E106" t="s">
-        <v>14</v>
-      </c>
-      <c r="F106" s="3" t="s">
-        <v>411</v>
       </c>
       <c r="G106">
         <v>10003</v>
@@ -8849,13 +8751,13 @@
         <v>209</v>
       </c>
       <c r="M106" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N106" t="s">
         <v>208</v>
       </c>
       <c r="O106" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P106" t="b">
         <v>0</v>
@@ -8869,19 +8771,19 @@
         <v>1111</v>
       </c>
       <c r="B107" t="s">
+        <v>411</v>
+      </c>
+      <c r="C107" t="s">
+        <v>411</v>
+      </c>
+      <c r="D107" t="s">
+        <v>13</v>
+      </c>
+      <c r="E107" t="s">
+        <v>14</v>
+      </c>
+      <c r="F107" s="3" t="s">
         <v>412</v>
-      </c>
-      <c r="C107" t="s">
-        <v>412</v>
-      </c>
-      <c r="D107" t="s">
-        <v>13</v>
-      </c>
-      <c r="E107" t="s">
-        <v>14</v>
-      </c>
-      <c r="F107" s="3" t="s">
-        <v>413</v>
       </c>
       <c r="G107">
         <v>10001</v>
@@ -8902,13 +8804,13 @@
         <v>209</v>
       </c>
       <c r="M107" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N107" t="s">
         <v>224</v>
       </c>
       <c r="O107" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P107" t="b">
         <v>0</v>
@@ -8922,19 +8824,19 @@
         <v>1121</v>
       </c>
       <c r="B108" t="s">
+        <v>413</v>
+      </c>
+      <c r="C108" t="s">
+        <v>413</v>
+      </c>
+      <c r="D108" t="s">
+        <v>13</v>
+      </c>
+      <c r="E108" t="s">
+        <v>14</v>
+      </c>
+      <c r="F108" s="3" t="s">
         <v>414</v>
-      </c>
-      <c r="C108" t="s">
-        <v>414</v>
-      </c>
-      <c r="D108" t="s">
-        <v>13</v>
-      </c>
-      <c r="E108" t="s">
-        <v>14</v>
-      </c>
-      <c r="F108" s="3" t="s">
-        <v>415</v>
       </c>
       <c r="G108">
         <v>10008</v>
@@ -8955,13 +8857,13 @@
         <v>209</v>
       </c>
       <c r="M108" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N108" t="s">
         <v>208</v>
       </c>
       <c r="O108" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P108" t="b">
         <v>0</v>
@@ -8975,10 +8877,10 @@
         <v>1125</v>
       </c>
       <c r="B109" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C109" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D109" t="s">
         <v>46</v>
@@ -8987,7 +8889,7 @@
         <v>14</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="G109">
         <v>10001</v>
@@ -9008,13 +8910,13 @@
         <v>209</v>
       </c>
       <c r="M109" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N109" t="s">
         <v>207</v>
       </c>
       <c r="O109" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P109" t="b">
         <v>0</v>
@@ -9028,19 +8930,19 @@
         <v>1126</v>
       </c>
       <c r="B110" t="s">
+        <v>417</v>
+      </c>
+      <c r="C110" t="s">
+        <v>417</v>
+      </c>
+      <c r="D110" t="s">
+        <v>13</v>
+      </c>
+      <c r="E110" t="s">
+        <v>14</v>
+      </c>
+      <c r="F110" t="s">
         <v>418</v>
-      </c>
-      <c r="C110" t="s">
-        <v>418</v>
-      </c>
-      <c r="D110" t="s">
-        <v>13</v>
-      </c>
-      <c r="E110" t="s">
-        <v>14</v>
-      </c>
-      <c r="F110" t="s">
-        <v>419</v>
       </c>
       <c r="G110">
         <v>10001</v>
@@ -9061,13 +8963,13 @@
         <v>209</v>
       </c>
       <c r="M110" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N110" t="s">
         <v>208</v>
       </c>
       <c r="O110" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P110" t="b">
         <v>0</v>
@@ -9081,19 +8983,19 @@
         <v>1127</v>
       </c>
       <c r="B111" t="s">
+        <v>419</v>
+      </c>
+      <c r="C111" t="s">
+        <v>419</v>
+      </c>
+      <c r="D111" t="s">
+        <v>13</v>
+      </c>
+      <c r="E111" t="s">
+        <v>14</v>
+      </c>
+      <c r="F111" t="s">
         <v>420</v>
-      </c>
-      <c r="C111" t="s">
-        <v>420</v>
-      </c>
-      <c r="D111" t="s">
-        <v>13</v>
-      </c>
-      <c r="E111" t="s">
-        <v>14</v>
-      </c>
-      <c r="F111" t="s">
-        <v>421</v>
       </c>
       <c r="G111">
         <v>10001</v>
@@ -9114,13 +9016,13 @@
         <v>209</v>
       </c>
       <c r="M111" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N111" t="s">
         <v>208</v>
       </c>
       <c r="O111" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P111" t="b">
         <v>0</v>
@@ -9134,19 +9036,19 @@
         <v>1132</v>
       </c>
       <c r="B112" t="s">
+        <v>421</v>
+      </c>
+      <c r="C112" t="s">
+        <v>421</v>
+      </c>
+      <c r="D112" t="s">
+        <v>13</v>
+      </c>
+      <c r="E112" t="s">
+        <v>14</v>
+      </c>
+      <c r="F112" t="s">
         <v>422</v>
-      </c>
-      <c r="C112" t="s">
-        <v>422</v>
-      </c>
-      <c r="D112" t="s">
-        <v>13</v>
-      </c>
-      <c r="E112" t="s">
-        <v>14</v>
-      </c>
-      <c r="F112" t="s">
-        <v>423</v>
       </c>
       <c r="G112">
         <v>10003</v>
@@ -9167,13 +9069,13 @@
         <v>209</v>
       </c>
       <c r="M112" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N112" t="s">
         <v>208</v>
       </c>
       <c r="O112" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P112" t="b">
         <v>0</v>
@@ -9187,19 +9089,19 @@
         <v>1133</v>
       </c>
       <c r="B113" t="s">
+        <v>423</v>
+      </c>
+      <c r="C113" t="s">
+        <v>423</v>
+      </c>
+      <c r="D113" t="s">
+        <v>13</v>
+      </c>
+      <c r="E113" t="s">
+        <v>14</v>
+      </c>
+      <c r="F113" s="3" t="s">
         <v>424</v>
-      </c>
-      <c r="C113" t="s">
-        <v>424</v>
-      </c>
-      <c r="D113" t="s">
-        <v>13</v>
-      </c>
-      <c r="E113" t="s">
-        <v>14</v>
-      </c>
-      <c r="F113" s="3" t="s">
-        <v>425</v>
       </c>
       <c r="G113">
         <v>10003</v>
@@ -9220,13 +9122,13 @@
         <v>209</v>
       </c>
       <c r="M113" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N113" t="s">
         <v>208</v>
       </c>
       <c r="O113" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P113" t="b">
         <v>0</v>
@@ -9240,19 +9142,19 @@
         <v>1135</v>
       </c>
       <c r="B114" t="s">
+        <v>425</v>
+      </c>
+      <c r="C114" t="s">
+        <v>425</v>
+      </c>
+      <c r="D114" t="s">
+        <v>13</v>
+      </c>
+      <c r="E114" t="s">
+        <v>14</v>
+      </c>
+      <c r="F114" t="s">
         <v>426</v>
-      </c>
-      <c r="C114" t="s">
-        <v>426</v>
-      </c>
-      <c r="D114" t="s">
-        <v>13</v>
-      </c>
-      <c r="E114" t="s">
-        <v>14</v>
-      </c>
-      <c r="F114" t="s">
-        <v>427</v>
       </c>
       <c r="G114">
         <v>10003</v>
@@ -9273,13 +9175,13 @@
         <v>209</v>
       </c>
       <c r="M114" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N114" t="s">
         <v>208</v>
       </c>
       <c r="O114" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P114" t="b">
         <v>0</v>
@@ -9305,7 +9207,7 @@
         <v>14</v>
       </c>
       <c r="F115" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G115">
         <v>10001</v>
@@ -9326,13 +9228,13 @@
         <v>209</v>
       </c>
       <c r="M115" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N115" t="s">
         <v>208</v>
       </c>
       <c r="O115" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P115" t="b">
         <v>0</v>
@@ -9358,7 +9260,7 @@
         <v>14</v>
       </c>
       <c r="F116" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="G116">
         <v>10001</v>
@@ -9379,13 +9281,13 @@
         <v>209</v>
       </c>
       <c r="M116" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N116" t="s">
         <v>208</v>
       </c>
       <c r="O116" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P116" t="b">
         <v>0</v>
@@ -9399,19 +9301,19 @@
         <v>1151</v>
       </c>
       <c r="B117" t="s">
+        <v>429</v>
+      </c>
+      <c r="C117" t="s">
+        <v>429</v>
+      </c>
+      <c r="D117" t="s">
+        <v>13</v>
+      </c>
+      <c r="E117" t="s">
+        <v>14</v>
+      </c>
+      <c r="F117" t="s">
         <v>430</v>
-      </c>
-      <c r="C117" t="s">
-        <v>430</v>
-      </c>
-      <c r="D117" t="s">
-        <v>13</v>
-      </c>
-      <c r="E117" t="s">
-        <v>14</v>
-      </c>
-      <c r="F117" t="s">
-        <v>431</v>
       </c>
       <c r="G117">
         <v>10004</v>
@@ -9432,13 +9334,13 @@
         <v>209</v>
       </c>
       <c r="M117" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N117" t="s">
         <v>207</v>
       </c>
       <c r="O117" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P117" t="b">
         <v>0</v>
@@ -9452,19 +9354,19 @@
         <v>1152</v>
       </c>
       <c r="B118" t="s">
+        <v>431</v>
+      </c>
+      <c r="C118" t="s">
+        <v>431</v>
+      </c>
+      <c r="D118" t="s">
+        <v>13</v>
+      </c>
+      <c r="E118" t="s">
+        <v>14</v>
+      </c>
+      <c r="F118" t="s">
         <v>432</v>
-      </c>
-      <c r="C118" t="s">
-        <v>432</v>
-      </c>
-      <c r="D118" t="s">
-        <v>13</v>
-      </c>
-      <c r="E118" t="s">
-        <v>14</v>
-      </c>
-      <c r="F118" t="s">
-        <v>433</v>
       </c>
       <c r="G118">
         <v>10004</v>
@@ -9485,13 +9387,13 @@
         <v>209</v>
       </c>
       <c r="M118" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N118" t="s">
         <v>208</v>
       </c>
       <c r="O118" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P118" t="b">
         <v>0</v>
@@ -9505,19 +9407,19 @@
         <v>1159</v>
       </c>
       <c r="B119" t="s">
+        <v>433</v>
+      </c>
+      <c r="C119" t="s">
+        <v>433</v>
+      </c>
+      <c r="D119" t="s">
+        <v>13</v>
+      </c>
+      <c r="E119" t="s">
+        <v>14</v>
+      </c>
+      <c r="F119" t="s">
         <v>434</v>
-      </c>
-      <c r="C119" t="s">
-        <v>434</v>
-      </c>
-      <c r="D119" t="s">
-        <v>13</v>
-      </c>
-      <c r="E119" t="s">
-        <v>14</v>
-      </c>
-      <c r="F119" t="s">
-        <v>435</v>
       </c>
       <c r="G119">
         <v>10001</v>
@@ -9538,13 +9440,13 @@
         <v>209</v>
       </c>
       <c r="M119" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N119" t="s">
         <v>208</v>
       </c>
       <c r="O119" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P119" t="b">
         <v>0</v>
@@ -9558,19 +9460,19 @@
         <v>1161</v>
       </c>
       <c r="B120" t="s">
+        <v>435</v>
+      </c>
+      <c r="C120" t="s">
+        <v>435</v>
+      </c>
+      <c r="D120" t="s">
+        <v>13</v>
+      </c>
+      <c r="E120" t="s">
+        <v>14</v>
+      </c>
+      <c r="F120" s="3" t="s">
         <v>436</v>
-      </c>
-      <c r="C120" t="s">
-        <v>436</v>
-      </c>
-      <c r="D120" t="s">
-        <v>13</v>
-      </c>
-      <c r="E120" t="s">
-        <v>14</v>
-      </c>
-      <c r="F120" s="3" t="s">
-        <v>437</v>
       </c>
       <c r="G120">
         <v>10003</v>
@@ -9591,13 +9493,13 @@
         <v>209</v>
       </c>
       <c r="M120" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N120" t="s">
         <v>208</v>
       </c>
       <c r="O120" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P120" t="b">
         <v>0</v>
@@ -9611,19 +9513,19 @@
         <v>1228</v>
       </c>
       <c r="B121" t="s">
+        <v>437</v>
+      </c>
+      <c r="C121" t="s">
+        <v>437</v>
+      </c>
+      <c r="D121" t="s">
+        <v>13</v>
+      </c>
+      <c r="E121" t="s">
+        <v>14</v>
+      </c>
+      <c r="F121" t="s">
         <v>438</v>
-      </c>
-      <c r="C121" t="s">
-        <v>438</v>
-      </c>
-      <c r="D121" t="s">
-        <v>13</v>
-      </c>
-      <c r="E121" t="s">
-        <v>14</v>
-      </c>
-      <c r="F121" t="s">
-        <v>439</v>
       </c>
       <c r="G121">
         <v>10003</v>
@@ -9644,13 +9546,13 @@
         <v>209</v>
       </c>
       <c r="M121" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N121" t="s">
         <v>208</v>
       </c>
       <c r="O121" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P121" t="b">
         <v>0</v>
@@ -9664,10 +9566,10 @@
         <v>1229</v>
       </c>
       <c r="B122" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C122" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D122" t="s">
         <v>13</v>
@@ -9697,13 +9599,13 @@
         <v>209</v>
       </c>
       <c r="M122" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N122" t="s">
         <v>208</v>
       </c>
       <c r="O122" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P122" t="b">
         <v>0</v>
@@ -9717,19 +9619,19 @@
         <v>1230</v>
       </c>
       <c r="B123" t="s">
+        <v>440</v>
+      </c>
+      <c r="C123" t="s">
+        <v>440</v>
+      </c>
+      <c r="D123" t="s">
+        <v>13</v>
+      </c>
+      <c r="E123" t="s">
+        <v>14</v>
+      </c>
+      <c r="F123" t="s">
         <v>441</v>
-      </c>
-      <c r="C123" t="s">
-        <v>441</v>
-      </c>
-      <c r="D123" t="s">
-        <v>13</v>
-      </c>
-      <c r="E123" t="s">
-        <v>14</v>
-      </c>
-      <c r="F123" t="s">
-        <v>442</v>
       </c>
       <c r="G123">
         <v>10003</v>
@@ -9750,13 +9652,13 @@
         <v>209</v>
       </c>
       <c r="M123" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N123" t="s">
         <v>208</v>
       </c>
       <c r="O123" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P123" t="b">
         <v>0</v>
@@ -9770,19 +9672,19 @@
         <v>1231</v>
       </c>
       <c r="B124" t="s">
+        <v>442</v>
+      </c>
+      <c r="C124" t="s">
+        <v>442</v>
+      </c>
+      <c r="D124" t="s">
+        <v>13</v>
+      </c>
+      <c r="E124" t="s">
+        <v>14</v>
+      </c>
+      <c r="F124" t="s">
         <v>443</v>
-      </c>
-      <c r="C124" t="s">
-        <v>443</v>
-      </c>
-      <c r="D124" t="s">
-        <v>13</v>
-      </c>
-      <c r="E124" t="s">
-        <v>14</v>
-      </c>
-      <c r="F124" t="s">
-        <v>444</v>
       </c>
       <c r="G124">
         <v>10003</v>
@@ -9803,13 +9705,13 @@
         <v>209</v>
       </c>
       <c r="M124" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N124" t="s">
         <v>208</v>
       </c>
       <c r="O124" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P124" t="b">
         <v>0</v>
@@ -9826,7 +9728,7 @@
         <v>313</v>
       </c>
       <c r="C125" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D125" t="s">
         <v>46</v>
@@ -9835,7 +9737,7 @@
         <v>14</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="G125">
         <v>10002</v>
@@ -9856,13 +9758,13 @@
         <v>209</v>
       </c>
       <c r="M125" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N125" t="s">
         <v>207</v>
       </c>
       <c r="O125" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P125" t="b">
         <v>0</v>
@@ -9876,19 +9778,19 @@
         <v>1174</v>
       </c>
       <c r="B126" t="s">
+        <v>446</v>
+      </c>
+      <c r="C126" t="s">
+        <v>446</v>
+      </c>
+      <c r="D126" t="s">
+        <v>13</v>
+      </c>
+      <c r="E126" t="s">
+        <v>14</v>
+      </c>
+      <c r="F126" t="s">
         <v>447</v>
-      </c>
-      <c r="C126" t="s">
-        <v>447</v>
-      </c>
-      <c r="D126" t="s">
-        <v>13</v>
-      </c>
-      <c r="E126" t="s">
-        <v>14</v>
-      </c>
-      <c r="F126" t="s">
-        <v>448</v>
       </c>
       <c r="G126">
         <v>10006</v>
@@ -9909,13 +9811,13 @@
         <v>209</v>
       </c>
       <c r="M126" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N126" t="s">
         <v>208</v>
       </c>
       <c r="O126" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P126" t="b">
         <v>0</v>
@@ -9929,19 +9831,19 @@
         <v>1175</v>
       </c>
       <c r="B127" t="s">
+        <v>448</v>
+      </c>
+      <c r="C127" t="s">
+        <v>448</v>
+      </c>
+      <c r="D127" t="s">
+        <v>13</v>
+      </c>
+      <c r="E127" t="s">
+        <v>14</v>
+      </c>
+      <c r="F127" t="s">
         <v>449</v>
-      </c>
-      <c r="C127" t="s">
-        <v>449</v>
-      </c>
-      <c r="D127" t="s">
-        <v>13</v>
-      </c>
-      <c r="E127" t="s">
-        <v>14</v>
-      </c>
-      <c r="F127" t="s">
-        <v>450</v>
       </c>
       <c r="G127">
         <v>10006</v>
@@ -9962,13 +9864,13 @@
         <v>209</v>
       </c>
       <c r="M127" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N127" t="s">
         <v>208</v>
       </c>
       <c r="O127" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P127" t="b">
         <v>0</v>
@@ -9982,10 +9884,10 @@
         <v>1176</v>
       </c>
       <c r="B128" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C128" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D128" t="s">
         <v>13</v>
@@ -10015,13 +9917,13 @@
         <v>209</v>
       </c>
       <c r="M128" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N128" t="s">
         <v>208</v>
       </c>
       <c r="O128" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P128" t="b">
         <v>0</v>
@@ -10035,19 +9937,19 @@
         <v>1177</v>
       </c>
       <c r="B129" t="s">
+        <v>451</v>
+      </c>
+      <c r="C129" t="s">
+        <v>451</v>
+      </c>
+      <c r="D129" t="s">
+        <v>13</v>
+      </c>
+      <c r="E129" t="s">
+        <v>14</v>
+      </c>
+      <c r="F129" t="s">
         <v>452</v>
-      </c>
-      <c r="C129" t="s">
-        <v>452</v>
-      </c>
-      <c r="D129" t="s">
-        <v>13</v>
-      </c>
-      <c r="E129" t="s">
-        <v>14</v>
-      </c>
-      <c r="F129" t="s">
-        <v>453</v>
       </c>
       <c r="G129">
         <v>10006</v>
@@ -10068,13 +9970,13 @@
         <v>209</v>
       </c>
       <c r="M129" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N129" t="s">
         <v>208</v>
       </c>
       <c r="O129" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P129" t="b">
         <v>0</v>
@@ -10088,10 +9990,10 @@
         <v>1178</v>
       </c>
       <c r="B130" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C130" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D130" t="s">
         <v>13</v>
@@ -10121,13 +10023,13 @@
         <v>209</v>
       </c>
       <c r="M130" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N130" t="s">
         <v>208</v>
       </c>
       <c r="O130" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P130" t="b">
         <v>0</v>
@@ -10141,10 +10043,10 @@
         <v>1179</v>
       </c>
       <c r="B131" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C131" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D131" t="s">
         <v>13</v>
@@ -10174,13 +10076,13 @@
         <v>209</v>
       </c>
       <c r="M131" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N131" t="s">
         <v>208</v>
       </c>
       <c r="O131" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P131" t="b">
         <v>0</v>
@@ -10194,19 +10096,19 @@
         <v>1180</v>
       </c>
       <c r="B132" t="s">
+        <v>455</v>
+      </c>
+      <c r="C132" t="s">
+        <v>455</v>
+      </c>
+      <c r="D132" t="s">
+        <v>13</v>
+      </c>
+      <c r="E132" t="s">
+        <v>14</v>
+      </c>
+      <c r="F132" t="s">
         <v>456</v>
-      </c>
-      <c r="C132" t="s">
-        <v>456</v>
-      </c>
-      <c r="D132" t="s">
-        <v>13</v>
-      </c>
-      <c r="E132" t="s">
-        <v>14</v>
-      </c>
-      <c r="F132" t="s">
-        <v>457</v>
       </c>
       <c r="G132">
         <v>10006</v>
@@ -10227,13 +10129,13 @@
         <v>209</v>
       </c>
       <c r="M132" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N132" t="s">
         <v>208</v>
       </c>
       <c r="O132" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P132" t="b">
         <v>0</v>
@@ -10247,19 +10149,19 @@
         <v>1181</v>
       </c>
       <c r="B133" t="s">
+        <v>457</v>
+      </c>
+      <c r="C133" t="s">
+        <v>457</v>
+      </c>
+      <c r="D133" t="s">
+        <v>13</v>
+      </c>
+      <c r="E133" t="s">
+        <v>14</v>
+      </c>
+      <c r="F133" t="s">
         <v>458</v>
-      </c>
-      <c r="C133" t="s">
-        <v>458</v>
-      </c>
-      <c r="D133" t="s">
-        <v>13</v>
-      </c>
-      <c r="E133" t="s">
-        <v>14</v>
-      </c>
-      <c r="F133" t="s">
-        <v>459</v>
       </c>
       <c r="G133">
         <v>10006</v>
@@ -10280,13 +10182,13 @@
         <v>209</v>
       </c>
       <c r="M133" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N133" t="s">
         <v>208</v>
       </c>
       <c r="O133" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P133" t="b">
         <v>0</v>
@@ -10300,10 +10202,10 @@
         <v>1182</v>
       </c>
       <c r="B134" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C134" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D134" t="s">
         <v>13</v>
@@ -10333,13 +10235,13 @@
         <v>209</v>
       </c>
       <c r="M134" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N134" t="s">
         <v>208</v>
       </c>
       <c r="O134" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P134" t="b">
         <v>0</v>
@@ -10353,10 +10255,10 @@
         <v>1183</v>
       </c>
       <c r="B135" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C135" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D135" t="s">
         <v>13</v>
@@ -10386,13 +10288,13 @@
         <v>209</v>
       </c>
       <c r="M135" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N135" t="s">
         <v>208</v>
       </c>
       <c r="O135" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P135" t="b">
         <v>0</v>
@@ -10406,10 +10308,10 @@
         <v>1184</v>
       </c>
       <c r="B136" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C136" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D136" t="s">
         <v>13</v>
@@ -10439,13 +10341,13 @@
         <v>209</v>
       </c>
       <c r="M136" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N136" t="s">
         <v>208</v>
       </c>
       <c r="O136" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P136" t="b">
         <v>0</v>
@@ -10459,10 +10361,10 @@
         <v>1185</v>
       </c>
       <c r="B137" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C137" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D137" t="s">
         <v>13</v>
@@ -10492,13 +10394,13 @@
         <v>209</v>
       </c>
       <c r="M137" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N137" t="s">
         <v>208</v>
       </c>
       <c r="O137" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P137" t="b">
         <v>0</v>
@@ -10512,19 +10414,19 @@
         <v>1186</v>
       </c>
       <c r="B138" t="s">
+        <v>463</v>
+      </c>
+      <c r="C138" t="s">
+        <v>463</v>
+      </c>
+      <c r="D138" t="s">
+        <v>13</v>
+      </c>
+      <c r="E138" t="s">
+        <v>14</v>
+      </c>
+      <c r="F138" t="s">
         <v>464</v>
-      </c>
-      <c r="C138" t="s">
-        <v>464</v>
-      </c>
-      <c r="D138" t="s">
-        <v>13</v>
-      </c>
-      <c r="E138" t="s">
-        <v>14</v>
-      </c>
-      <c r="F138" t="s">
-        <v>465</v>
       </c>
       <c r="G138">
         <v>10006</v>
@@ -10545,13 +10447,13 @@
         <v>209</v>
       </c>
       <c r="M138" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N138" t="s">
         <v>208</v>
       </c>
       <c r="O138" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P138" t="b">
         <v>0</v>
@@ -10577,7 +10479,7 @@
         <v>14</v>
       </c>
       <c r="F139" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="G139">
         <v>10006</v>
@@ -10598,13 +10500,13 @@
         <v>209</v>
       </c>
       <c r="M139" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N139" t="s">
         <v>208</v>
       </c>
       <c r="O139" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P139" t="b">
         <v>0</v>
@@ -10618,19 +10520,19 @@
         <v>1188</v>
       </c>
       <c r="B140" t="s">
+        <v>466</v>
+      </c>
+      <c r="C140" t="s">
+        <v>466</v>
+      </c>
+      <c r="D140" t="s">
+        <v>13</v>
+      </c>
+      <c r="E140" t="s">
+        <v>14</v>
+      </c>
+      <c r="F140" t="s">
         <v>467</v>
-      </c>
-      <c r="C140" t="s">
-        <v>467</v>
-      </c>
-      <c r="D140" t="s">
-        <v>13</v>
-      </c>
-      <c r="E140" t="s">
-        <v>14</v>
-      </c>
-      <c r="F140" t="s">
-        <v>468</v>
       </c>
       <c r="G140">
         <v>10006</v>
@@ -10651,13 +10553,13 @@
         <v>209</v>
       </c>
       <c r="M140" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N140" t="s">
         <v>208</v>
       </c>
       <c r="O140" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P140" t="b">
         <v>0</v>
@@ -10683,7 +10585,7 @@
         <v>14</v>
       </c>
       <c r="F141" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="G141">
         <v>10006</v>
@@ -10704,13 +10606,13 @@
         <v>209</v>
       </c>
       <c r="M141" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N141" t="s">
         <v>208</v>
       </c>
       <c r="O141" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P141" t="b">
         <v>0</v>
@@ -10724,10 +10626,10 @@
         <v>1190</v>
       </c>
       <c r="B142" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C142" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D142" t="s">
         <v>13</v>
@@ -10757,13 +10659,13 @@
         <v>209</v>
       </c>
       <c r="M142" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N142" t="s">
         <v>208</v>
       </c>
       <c r="O142" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P142" t="b">
         <v>0</v>
@@ -10777,10 +10679,10 @@
         <v>1191</v>
       </c>
       <c r="B143" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C143" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D143" t="s">
         <v>13</v>
@@ -10810,13 +10712,13 @@
         <v>209</v>
       </c>
       <c r="M143" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N143" t="s">
         <v>208</v>
       </c>
       <c r="O143" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P143" t="b">
         <v>0</v>
@@ -10830,19 +10732,19 @@
         <v>1192</v>
       </c>
       <c r="B144" t="s">
+        <v>471</v>
+      </c>
+      <c r="C144" t="s">
+        <v>471</v>
+      </c>
+      <c r="D144" t="s">
+        <v>13</v>
+      </c>
+      <c r="E144" t="s">
+        <v>14</v>
+      </c>
+      <c r="F144" t="s">
         <v>472</v>
-      </c>
-      <c r="C144" t="s">
-        <v>472</v>
-      </c>
-      <c r="D144" t="s">
-        <v>13</v>
-      </c>
-      <c r="E144" t="s">
-        <v>14</v>
-      </c>
-      <c r="F144" t="s">
-        <v>473</v>
       </c>
       <c r="G144">
         <v>10006</v>
@@ -10863,13 +10765,13 @@
         <v>209</v>
       </c>
       <c r="M144" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N144" t="s">
         <v>208</v>
       </c>
       <c r="O144" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P144" t="b">
         <v>0</v>
@@ -10883,19 +10785,19 @@
         <v>1193</v>
       </c>
       <c r="B145" t="s">
+        <v>473</v>
+      </c>
+      <c r="C145" t="s">
+        <v>473</v>
+      </c>
+      <c r="D145" t="s">
+        <v>13</v>
+      </c>
+      <c r="E145" t="s">
+        <v>14</v>
+      </c>
+      <c r="F145" t="s">
         <v>474</v>
-      </c>
-      <c r="C145" t="s">
-        <v>474</v>
-      </c>
-      <c r="D145" t="s">
-        <v>13</v>
-      </c>
-      <c r="E145" t="s">
-        <v>14</v>
-      </c>
-      <c r="F145" t="s">
-        <v>475</v>
       </c>
       <c r="G145">
         <v>10006</v>
@@ -10916,13 +10818,13 @@
         <v>209</v>
       </c>
       <c r="M145" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N145" t="s">
         <v>208</v>
       </c>
       <c r="O145" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P145" t="b">
         <v>0</v>
@@ -10936,10 +10838,10 @@
         <v>1194</v>
       </c>
       <c r="B146" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C146" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D146" t="s">
         <v>13</v>
@@ -10969,13 +10871,13 @@
         <v>209</v>
       </c>
       <c r="M146" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N146" t="s">
         <v>208</v>
       </c>
       <c r="O146" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P146" t="b">
         <v>0</v>
@@ -10989,19 +10891,19 @@
         <v>1195</v>
       </c>
       <c r="B147" t="s">
+        <v>476</v>
+      </c>
+      <c r="C147" t="s">
+        <v>476</v>
+      </c>
+      <c r="D147" t="s">
+        <v>13</v>
+      </c>
+      <c r="E147" t="s">
+        <v>14</v>
+      </c>
+      <c r="F147" t="s">
         <v>477</v>
-      </c>
-      <c r="C147" t="s">
-        <v>477</v>
-      </c>
-      <c r="D147" t="s">
-        <v>13</v>
-      </c>
-      <c r="E147" t="s">
-        <v>14</v>
-      </c>
-      <c r="F147" t="s">
-        <v>478</v>
       </c>
       <c r="G147">
         <v>10006</v>
@@ -11022,13 +10924,13 @@
         <v>209</v>
       </c>
       <c r="M147" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N147" t="s">
         <v>208</v>
       </c>
       <c r="O147" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P147" t="b">
         <v>0</v>
@@ -11042,10 +10944,10 @@
         <v>1196</v>
       </c>
       <c r="B148" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C148" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D148" t="s">
         <v>13</v>
@@ -11075,13 +10977,13 @@
         <v>209</v>
       </c>
       <c r="M148" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N148" t="s">
         <v>208</v>
       </c>
       <c r="O148" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P148" t="b">
         <v>0</v>
@@ -11095,10 +10997,10 @@
         <v>1197</v>
       </c>
       <c r="B149" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C149" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D149" t="s">
         <v>13</v>
@@ -11128,13 +11030,13 @@
         <v>209</v>
       </c>
       <c r="M149" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N149" t="s">
         <v>208</v>
       </c>
       <c r="O149" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P149" t="b">
         <v>0</v>
@@ -11148,19 +11050,19 @@
         <v>1198</v>
       </c>
       <c r="B150" t="s">
+        <v>480</v>
+      </c>
+      <c r="C150" t="s">
+        <v>480</v>
+      </c>
+      <c r="D150" t="s">
+        <v>13</v>
+      </c>
+      <c r="E150" t="s">
+        <v>14</v>
+      </c>
+      <c r="F150" t="s">
         <v>481</v>
-      </c>
-      <c r="C150" t="s">
-        <v>481</v>
-      </c>
-      <c r="D150" t="s">
-        <v>13</v>
-      </c>
-      <c r="E150" t="s">
-        <v>14</v>
-      </c>
-      <c r="F150" t="s">
-        <v>482</v>
       </c>
       <c r="G150">
         <v>10006</v>
@@ -11181,13 +11083,13 @@
         <v>209</v>
       </c>
       <c r="M150" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N150" t="s">
         <v>208</v>
       </c>
       <c r="O150" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P150" t="b">
         <v>0</v>
@@ -11201,19 +11103,19 @@
         <v>1199</v>
       </c>
       <c r="B151" t="s">
+        <v>482</v>
+      </c>
+      <c r="C151" t="s">
+        <v>482</v>
+      </c>
+      <c r="D151" t="s">
+        <v>13</v>
+      </c>
+      <c r="E151" t="s">
+        <v>14</v>
+      </c>
+      <c r="F151" t="s">
         <v>483</v>
-      </c>
-      <c r="C151" t="s">
-        <v>483</v>
-      </c>
-      <c r="D151" t="s">
-        <v>13</v>
-      </c>
-      <c r="E151" t="s">
-        <v>14</v>
-      </c>
-      <c r="F151" t="s">
-        <v>484</v>
       </c>
       <c r="G151">
         <v>10006</v>
@@ -11234,13 +11136,13 @@
         <v>209</v>
       </c>
       <c r="M151" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N151" t="s">
         <v>208</v>
       </c>
       <c r="O151" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P151" t="b">
         <v>0</v>
@@ -11254,19 +11156,19 @@
         <v>1201</v>
       </c>
       <c r="B152" t="s">
+        <v>484</v>
+      </c>
+      <c r="C152" t="s">
+        <v>484</v>
+      </c>
+      <c r="D152" t="s">
+        <v>13</v>
+      </c>
+      <c r="E152" t="s">
+        <v>14</v>
+      </c>
+      <c r="F152" t="s">
         <v>485</v>
-      </c>
-      <c r="C152" t="s">
-        <v>485</v>
-      </c>
-      <c r="D152" t="s">
-        <v>13</v>
-      </c>
-      <c r="E152" t="s">
-        <v>14</v>
-      </c>
-      <c r="F152" t="s">
-        <v>486</v>
       </c>
       <c r="G152">
         <v>10006</v>
@@ -11287,13 +11189,13 @@
         <v>209</v>
       </c>
       <c r="M152" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N152" t="s">
         <v>208</v>
       </c>
       <c r="O152" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P152" t="b">
         <v>0</v>
@@ -11307,10 +11209,10 @@
         <v>1202</v>
       </c>
       <c r="B153" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C153" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D153" t="s">
         <v>13</v>
@@ -11340,13 +11242,13 @@
         <v>209</v>
       </c>
       <c r="M153" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N153" t="s">
         <v>208</v>
       </c>
       <c r="O153" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P153" t="b">
         <v>0</v>
@@ -11360,10 +11262,10 @@
         <v>1203</v>
       </c>
       <c r="B154" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C154" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D154" t="s">
         <v>13</v>
@@ -11393,13 +11295,13 @@
         <v>209</v>
       </c>
       <c r="M154" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N154" t="s">
         <v>208</v>
       </c>
       <c r="O154" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P154" t="b">
         <v>0</v>
@@ -11413,19 +11315,19 @@
         <v>1204</v>
       </c>
       <c r="B155" t="s">
+        <v>488</v>
+      </c>
+      <c r="C155" t="s">
+        <v>488</v>
+      </c>
+      <c r="D155" t="s">
+        <v>13</v>
+      </c>
+      <c r="E155" t="s">
+        <v>14</v>
+      </c>
+      <c r="F155" t="s">
         <v>489</v>
-      </c>
-      <c r="C155" t="s">
-        <v>489</v>
-      </c>
-      <c r="D155" t="s">
-        <v>13</v>
-      </c>
-      <c r="E155" t="s">
-        <v>14</v>
-      </c>
-      <c r="F155" t="s">
-        <v>490</v>
       </c>
       <c r="G155">
         <v>10006</v>
@@ -11446,13 +11348,13 @@
         <v>209</v>
       </c>
       <c r="M155" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N155" t="s">
         <v>208</v>
       </c>
       <c r="O155" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P155" t="b">
         <v>0</v>
@@ -11466,19 +11368,19 @@
         <v>1205</v>
       </c>
       <c r="B156" t="s">
+        <v>490</v>
+      </c>
+      <c r="C156" t="s">
+        <v>490</v>
+      </c>
+      <c r="D156" t="s">
+        <v>13</v>
+      </c>
+      <c r="E156" t="s">
+        <v>14</v>
+      </c>
+      <c r="F156" t="s">
         <v>491</v>
-      </c>
-      <c r="C156" t="s">
-        <v>491</v>
-      </c>
-      <c r="D156" t="s">
-        <v>13</v>
-      </c>
-      <c r="E156" t="s">
-        <v>14</v>
-      </c>
-      <c r="F156" t="s">
-        <v>492</v>
       </c>
       <c r="G156">
         <v>10006</v>
@@ -11499,13 +11401,13 @@
         <v>209</v>
       </c>
       <c r="M156" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N156" t="s">
         <v>208</v>
       </c>
       <c r="O156" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P156" t="b">
         <v>0</v>
@@ -11519,19 +11421,19 @@
         <v>1206</v>
       </c>
       <c r="B157" t="s">
+        <v>492</v>
+      </c>
+      <c r="C157" t="s">
+        <v>492</v>
+      </c>
+      <c r="D157" t="s">
+        <v>13</v>
+      </c>
+      <c r="E157" t="s">
+        <v>14</v>
+      </c>
+      <c r="F157" t="s">
         <v>493</v>
-      </c>
-      <c r="C157" t="s">
-        <v>493</v>
-      </c>
-      <c r="D157" t="s">
-        <v>13</v>
-      </c>
-      <c r="E157" t="s">
-        <v>14</v>
-      </c>
-      <c r="F157" t="s">
-        <v>494</v>
       </c>
       <c r="G157">
         <v>10006</v>
@@ -11552,13 +11454,13 @@
         <v>209</v>
       </c>
       <c r="M157" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N157" t="s">
         <v>208</v>
       </c>
       <c r="O157" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P157" t="b">
         <v>0</v>
@@ -11572,19 +11474,19 @@
         <v>1207</v>
       </c>
       <c r="B158" t="s">
+        <v>494</v>
+      </c>
+      <c r="C158" t="s">
+        <v>494</v>
+      </c>
+      <c r="D158" t="s">
+        <v>13</v>
+      </c>
+      <c r="E158" t="s">
+        <v>14</v>
+      </c>
+      <c r="F158" t="s">
         <v>495</v>
-      </c>
-      <c r="C158" t="s">
-        <v>495</v>
-      </c>
-      <c r="D158" t="s">
-        <v>13</v>
-      </c>
-      <c r="E158" t="s">
-        <v>14</v>
-      </c>
-      <c r="F158" t="s">
-        <v>496</v>
       </c>
       <c r="G158">
         <v>10006</v>
@@ -11605,13 +11507,13 @@
         <v>209</v>
       </c>
       <c r="M158" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N158" t="s">
         <v>208</v>
       </c>
       <c r="O158" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P158" t="b">
         <v>0</v>
@@ -11625,19 +11527,19 @@
         <v>1208</v>
       </c>
       <c r="B159" t="s">
+        <v>496</v>
+      </c>
+      <c r="C159" t="s">
+        <v>496</v>
+      </c>
+      <c r="D159" t="s">
+        <v>13</v>
+      </c>
+      <c r="E159" t="s">
+        <v>14</v>
+      </c>
+      <c r="F159" t="s">
         <v>497</v>
-      </c>
-      <c r="C159" t="s">
-        <v>497</v>
-      </c>
-      <c r="D159" t="s">
-        <v>13</v>
-      </c>
-      <c r="E159" t="s">
-        <v>14</v>
-      </c>
-      <c r="F159" t="s">
-        <v>498</v>
       </c>
       <c r="G159">
         <v>10006</v>
@@ -11658,13 +11560,13 @@
         <v>209</v>
       </c>
       <c r="M159" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N159" t="s">
         <v>208</v>
       </c>
       <c r="O159" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P159" t="b">
         <v>0</v>
@@ -11678,19 +11580,19 @@
         <v>1209</v>
       </c>
       <c r="B160" t="s">
+        <v>498</v>
+      </c>
+      <c r="C160" t="s">
+        <v>498</v>
+      </c>
+      <c r="D160" t="s">
+        <v>13</v>
+      </c>
+      <c r="E160" t="s">
+        <v>14</v>
+      </c>
+      <c r="F160" t="s">
         <v>499</v>
-      </c>
-      <c r="C160" t="s">
-        <v>499</v>
-      </c>
-      <c r="D160" t="s">
-        <v>13</v>
-      </c>
-      <c r="E160" t="s">
-        <v>14</v>
-      </c>
-      <c r="F160" t="s">
-        <v>500</v>
       </c>
       <c r="G160">
         <v>10006</v>
@@ -11711,13 +11613,13 @@
         <v>209</v>
       </c>
       <c r="M160" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N160" t="s">
         <v>208</v>
       </c>
       <c r="O160" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P160" t="b">
         <v>0</v>
@@ -11731,10 +11633,10 @@
         <v>1240</v>
       </c>
       <c r="B161" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C161" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D161" t="s">
         <v>13</v>
@@ -11764,13 +11666,13 @@
         <v>209</v>
       </c>
       <c r="M161" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N161" t="s">
         <v>208</v>
       </c>
       <c r="O161" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P161" t="b">
         <v>0</v>
@@ -11784,19 +11686,19 @@
         <v>1241</v>
       </c>
       <c r="B162" t="s">
+        <v>501</v>
+      </c>
+      <c r="C162" t="s">
+        <v>501</v>
+      </c>
+      <c r="D162" t="s">
+        <v>13</v>
+      </c>
+      <c r="E162" t="s">
+        <v>14</v>
+      </c>
+      <c r="F162" t="s">
         <v>502</v>
-      </c>
-      <c r="C162" t="s">
-        <v>502</v>
-      </c>
-      <c r="D162" t="s">
-        <v>13</v>
-      </c>
-      <c r="E162" t="s">
-        <v>14</v>
-      </c>
-      <c r="F162" t="s">
-        <v>503</v>
       </c>
       <c r="G162">
         <v>10006</v>
@@ -11817,13 +11719,13 @@
         <v>209</v>
       </c>
       <c r="M162" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N162" t="s">
         <v>208</v>
       </c>
       <c r="O162" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P162" t="b">
         <v>0</v>
@@ -11837,10 +11739,10 @@
         <v>1243</v>
       </c>
       <c r="B163" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C163" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D163" t="s">
         <v>13</v>
@@ -11870,13 +11772,13 @@
         <v>209</v>
       </c>
       <c r="M163" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N163" t="s">
         <v>208</v>
       </c>
       <c r="O163" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P163" t="b">
         <v>0</v>
@@ -11890,10 +11792,10 @@
         <v>1260</v>
       </c>
       <c r="B164" t="s">
+        <v>504</v>
+      </c>
+      <c r="C164" t="s">
         <v>505</v>
-      </c>
-      <c r="C164" t="s">
-        <v>506</v>
       </c>
       <c r="D164" t="s">
         <v>13</v>
@@ -11923,13 +11825,13 @@
         <v>209</v>
       </c>
       <c r="M164" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N164" t="s">
         <v>208</v>
       </c>
       <c r="O164" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P164" t="b">
         <v>0</v>
@@ -11946,7 +11848,7 @@
         <v>217</v>
       </c>
       <c r="C165" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D165" t="s">
         <v>13</v>
@@ -11964,7 +11866,7 @@
         <v>187</v>
       </c>
       <c r="I165" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="J165" t="s">
         <v>206</v>
@@ -11976,13 +11878,13 @@
         <v>209</v>
       </c>
       <c r="M165" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N165" t="s">
         <v>208</v>
       </c>
       <c r="O165" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P165" t="b">
         <v>0</v>
@@ -11999,7 +11901,7 @@
         <v>218</v>
       </c>
       <c r="C166" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D166" t="s">
         <v>13</v>
@@ -12017,7 +11919,7 @@
         <v>187</v>
       </c>
       <c r="I166" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="J166" t="s">
         <v>206</v>
@@ -12029,13 +11931,13 @@
         <v>209</v>
       </c>
       <c r="M166" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N166" t="s">
         <v>208</v>
       </c>
       <c r="O166" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P166" t="b">
         <v>0</v>
@@ -12052,7 +11954,7 @@
         <v>219</v>
       </c>
       <c r="C167" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D167" t="s">
         <v>13</v>
@@ -12070,7 +11972,7 @@
         <v>187</v>
       </c>
       <c r="I167" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="J167" t="s">
         <v>206</v>
@@ -12082,13 +11984,13 @@
         <v>209</v>
       </c>
       <c r="M167" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N167" t="s">
         <v>208</v>
       </c>
       <c r="O167" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P167" t="b">
         <v>0</v>
@@ -12102,10 +12004,10 @@
         <v>1266</v>
       </c>
       <c r="B168" t="s">
+        <v>512</v>
+      </c>
+      <c r="C168" t="s">
         <v>513</v>
-      </c>
-      <c r="C168" t="s">
-        <v>514</v>
       </c>
       <c r="D168" t="s">
         <v>13</v>
@@ -12123,7 +12025,7 @@
         <v>187</v>
       </c>
       <c r="I168" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="J168" t="s">
         <v>206</v>
@@ -12135,13 +12037,13 @@
         <v>209</v>
       </c>
       <c r="M168" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N168" t="s">
         <v>208</v>
       </c>
       <c r="O168" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P168" t="b">
         <v>0</v>
@@ -12155,10 +12057,10 @@
         <v>1267</v>
       </c>
       <c r="B169" t="s">
+        <v>515</v>
+      </c>
+      <c r="C169" t="s">
         <v>516</v>
-      </c>
-      <c r="C169" t="s">
-        <v>517</v>
       </c>
       <c r="D169" t="s">
         <v>13</v>
@@ -12176,7 +12078,7 @@
         <v>187</v>
       </c>
       <c r="I169" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="J169" t="s">
         <v>206</v>
@@ -12188,13 +12090,13 @@
         <v>209</v>
       </c>
       <c r="M169" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N169" t="s">
         <v>208</v>
       </c>
       <c r="O169" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P169" t="b">
         <v>0</v>
@@ -12208,10 +12110,10 @@
         <v>1268</v>
       </c>
       <c r="B170" t="s">
+        <v>518</v>
+      </c>
+      <c r="C170" t="s">
         <v>519</v>
-      </c>
-      <c r="C170" t="s">
-        <v>520</v>
       </c>
       <c r="D170" t="s">
         <v>13</v>
@@ -12229,7 +12131,7 @@
         <v>187</v>
       </c>
       <c r="I170" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="J170" t="s">
         <v>206</v>
@@ -12241,13 +12143,13 @@
         <v>209</v>
       </c>
       <c r="M170" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N170" t="s">
         <v>208</v>
       </c>
       <c r="O170" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P170" t="b">
         <v>0</v>
@@ -12258,22 +12160,22 @@
     </row>
     <row r="171" spans="1:17" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A171" s="5" t="s">
+        <v>522</v>
+      </c>
+      <c r="B171" s="7" t="s">
         <v>523</v>
       </c>
-      <c r="B171" s="7" t="s">
+      <c r="C171" s="6" t="s">
         <v>524</v>
       </c>
-      <c r="C171" s="6" t="s">
+      <c r="D171" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E171" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F171" s="6" t="s">
         <v>525</v>
-      </c>
-      <c r="D171" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E171" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F171" s="6" t="s">
-        <v>526</v>
       </c>
       <c r="G171" s="5">
         <v>10002</v>
@@ -12282,25 +12184,25 @@
         <v>28</v>
       </c>
       <c r="I171" s="6" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="J171" s="6" t="s">
+        <v>526</v>
+      </c>
+      <c r="K171" s="4" t="s">
         <v>527</v>
       </c>
-      <c r="K171" s="4" t="s">
+      <c r="L171" s="6" t="s">
         <v>528</v>
       </c>
-      <c r="L171" s="6" t="s">
-        <v>529</v>
-      </c>
       <c r="M171" s="6" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N171" t="s">
         <v>208</v>
       </c>
       <c r="O171" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P171" t="b">
         <v>0</v>
@@ -12493,6 +12395,7 @@
     <row r="353" ht="14.5" x14ac:dyDescent="0.35"/>
     <row r="354" ht="14.5" x14ac:dyDescent="0.35"/>
   </sheetData>
+  <autoFilter ref="A1:Q171" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
